--- a/GMAX0505/Карта регистров_0505.xlsx
+++ b/GMAX0505/Карта регистров_0505.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agest\Downloads\Telegram Desktop\GMAX0505_LV\GMAX0505\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB000F7-34E1-4E44-8CA6-DA7CAD82413F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42B719A-1DBE-4C6F-AEDC-5502E60949E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -240,9 +240,6 @@
     <t>7F</t>
   </si>
   <si>
-    <t>0 бит = 1 стриминг</t>
-  </si>
-  <si>
     <t>Internal EXP</t>
   </si>
   <si>
@@ -266,6 +263,9 @@
   </si>
   <si>
     <t>Темпа</t>
+  </si>
+  <si>
+    <t>1 бит = 1 стриминг</t>
   </si>
 </sst>
 </file>
@@ -348,10 +348,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,7 +667,7 @@
         <v>52</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H1" t="s">
         <v>47</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -695,10 +695,10 @@
         <v>35</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1082,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="H19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -4409,8 +4409,8 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G194" s="10" t="s">
-        <v>79</v>
+      <c r="G194" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -4431,7 +4431,7 @@
         <f t="shared" ref="F195:F257" si="7">HEX2DEC(E195)</f>
         <v>0</v>
       </c>
-      <c r="G195" s="10"/>
+      <c r="G195" s="11"/>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
@@ -4702,7 +4702,7 @@
         <v>247</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
@@ -4766,7 +4766,7 @@
         <v>165</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
@@ -4844,13 +4844,13 @@
         <f t="shared" si="7"/>
         <v>221</v>
       </c>
-      <c r="G216" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H216" s="10"/>
-      <c r="I216" s="10"/>
-      <c r="J216" s="10"/>
-      <c r="K216" s="10"/>
+      <c r="G216" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H216" s="11"/>
+      <c r="I216" s="11"/>
+      <c r="J216" s="11"/>
+      <c r="K216" s="11"/>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
@@ -4870,11 +4870,11 @@
         <f t="shared" si="7"/>
         <v>13</v>
       </c>
-      <c r="G217" s="10"/>
-      <c r="H217" s="10"/>
-      <c r="I217" s="10"/>
-      <c r="J217" s="10"/>
-      <c r="K217" s="10"/>
+      <c r="G217" s="11"/>
+      <c r="H217" s="11"/>
+      <c r="I217" s="11"/>
+      <c r="J217" s="11"/>
+      <c r="K217" s="11"/>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
@@ -4894,11 +4894,11 @@
         <f t="shared" si="7"/>
         <v>211</v>
       </c>
-      <c r="G218" s="10"/>
-      <c r="H218" s="10"/>
-      <c r="I218" s="10"/>
-      <c r="J218" s="10"/>
-      <c r="K218" s="10"/>
+      <c r="G218" s="11"/>
+      <c r="H218" s="11"/>
+      <c r="I218" s="11"/>
+      <c r="J218" s="11"/>
+      <c r="K218" s="11"/>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
